--- a/Reports/AreDifferent/decryption_coldWater_byHouse2/decryption_coldWater_byHouse2.xlsx
+++ b/Reports/AreDifferent/decryption_coldWater_byHouse2/decryption_coldWater_byHouse2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\AreDifferent\decryption_coldWater_byHouse2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6457250B-DD79-48B4-9948-F2520715575C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="390" windowWidth="28440" windowHeight="12195"/>
+    <workbookView xWindow="180" yWindow="390" windowWidth="28440" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -14,18 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="259">
-  <si>
-    <t>Утверждаю :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">по жилищно-коммунальному хозяйству </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="250">
   <si>
     <t>Справка по расчету субсидий на холодное водоснабжение</t>
-  </si>
-  <si>
-    <t>ООО "ЭнергоКомпания"</t>
   </si>
   <si>
     <t>№ 
@@ -109,21 +106,6 @@
     <t>Баня</t>
   </si>
   <si>
-    <t>Подписи  :</t>
-  </si>
-  <si>
-    <t>Производитель:</t>
-  </si>
-  <si>
-    <t>Служба:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Директор МКУ "СЗ ЖКХ" </t>
-  </si>
-  <si>
-    <t>______________________ Д.В.Игошин</t>
-  </si>
-  <si>
     <t>Нач.ПЭО________________ Л.Д.Сафонова</t>
   </si>
   <si>
@@ -760,52 +742,49 @@
     <t>Начальник ПЭО</t>
   </si>
   <si>
-    <t>______________М.Е.Праздников</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ______________ Д.А.Соловьев</t>
-  </si>
-  <si>
     <t>$this-&gt;H['name_organization']</t>
   </si>
   <si>
     <t>"за ".$this-&gt;H['full_name_month']</t>
   </si>
   <si>
-    <t>И. о. заместителя Главы Беловского городского округа</t>
-  </si>
-  <si>
-    <t>(на осн.доверенности № 1/6733-8 от 13.12.2024)</t>
-  </si>
-  <si>
-    <t>___________________   Е. Т. Муратов</t>
-  </si>
-  <si>
-    <t>"______"_________________   2025</t>
-  </si>
-  <si>
-    <t>Вед.специалист по ВКХ_______________Н.А.Крюкова</t>
-  </si>
-  <si>
-    <t>Главный инженер</t>
-  </si>
-  <si>
-    <t>__________________  Е. В. Сикова</t>
-  </si>
-  <si>
-    <t>Приложение  к Соглашению № 30-юр  с 29.01.2025</t>
+    <t>Получатель субсидии:</t>
+  </si>
+  <si>
+    <t>Генеральный директор ООО"ЭК"________________ Игошин Д.В.</t>
+  </si>
+  <si>
+    <t>Вед.специалист по ВКХ________________ Н.А.Крюкова</t>
+  </si>
+  <si>
+    <t>Распорядитель субсидии:</t>
+  </si>
+  <si>
+    <t>Начальник УЖКиДК АБГО</t>
+  </si>
+  <si>
+    <t>Начальник ПТО</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ______________ Соловьев Д.А.</t>
+  </si>
+  <si>
+    <t>______________Кочегаров Д.В.</t>
+  </si>
+  <si>
+    <t>______________Праздников М.Е.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1385,116 +1364,124 @@
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 3" xfId="2"/>
-    <cellStyle name="Обычный_Водичка с 01.05. 2009г" xfId="3"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный_Водичка с 01.05. 2009г" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1784,12 +1771,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BI64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
@@ -1802,24 +1789,24 @@
     <col min="34" max="61" width="9.140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="24" customFormat="1">
+    <row r="1" spans="1:38" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AH1" s="24" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="AI1" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ1" s="24" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AK1" s="24">
         <v>19</v>
       </c>
       <c r="AL1" s="24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" s="24" customFormat="1" ht="18.75">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="52"/>
       <c r="B2" s="52"/>
       <c r="C2" s="52"/>
@@ -1834,9 +1821,7 @@
       <c r="L2" s="52"/>
       <c r="M2" s="52"/>
       <c r="N2" s="53"/>
-      <c r="O2" s="54" t="s">
-        <v>258</v>
-      </c>
+      <c r="O2" s="54"/>
       <c r="P2" s="53"/>
       <c r="Q2" s="53"/>
       <c r="R2" s="55"/>
@@ -1856,7 +1841,7 @@
       <c r="AF2" s="57"/>
       <c r="AG2" s="57"/>
     </row>
-    <row r="3" spans="1:38" s="24" customFormat="1">
+    <row r="3" spans="1:38" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="52"/>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -1891,7 +1876,7 @@
       <c r="AF3" s="59"/>
       <c r="AG3" s="59"/>
     </row>
-    <row r="4" spans="1:38" s="24" customFormat="1" ht="18.75">
+    <row r="4" spans="1:38" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="52"/>
       <c r="B4" s="52"/>
       <c r="C4" s="52"/>
@@ -1906,9 +1891,7 @@
       <c r="L4" s="52"/>
       <c r="M4" s="52"/>
       <c r="N4" s="52"/>
-      <c r="O4" s="60" t="s">
-        <v>0</v>
-      </c>
+      <c r="O4" s="60"/>
       <c r="P4" s="52"/>
       <c r="R4" s="26"/>
       <c r="S4" s="26"/>
@@ -1927,7 +1910,7 @@
       <c r="AF4" s="61"/>
       <c r="AG4" s="61"/>
     </row>
-    <row r="5" spans="1:38" s="24" customFormat="1" ht="18.75">
+    <row r="5" spans="1:38" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="52"/>
       <c r="B5" s="52"/>
       <c r="C5" s="52"/>
@@ -1942,9 +1925,7 @@
       <c r="L5" s="52"/>
       <c r="M5" s="52"/>
       <c r="N5" s="52"/>
-      <c r="O5" s="60" t="s">
-        <v>251</v>
-      </c>
+      <c r="O5" s="60"/>
       <c r="P5" s="52"/>
       <c r="R5" s="26"/>
       <c r="S5" s="26"/>
@@ -1963,7 +1944,7 @@
       <c r="AF5" s="61"/>
       <c r="AG5" s="61"/>
     </row>
-    <row r="6" spans="1:38" s="24" customFormat="1" ht="18.75">
+    <row r="6" spans="1:38" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="52"/>
       <c r="B6" s="52"/>
       <c r="C6" s="52"/>
@@ -1978,9 +1959,7 @@
       <c r="L6" s="52"/>
       <c r="M6" s="52"/>
       <c r="N6" s="52"/>
-      <c r="O6" s="60" t="s">
-        <v>1</v>
-      </c>
+      <c r="O6" s="60"/>
       <c r="P6" s="52"/>
       <c r="R6" s="26"/>
       <c r="S6" s="26"/>
@@ -1999,7 +1978,7 @@
       <c r="AF6" s="61"/>
       <c r="AG6" s="61"/>
     </row>
-    <row r="7" spans="1:38" s="24" customFormat="1" ht="18.75">
+    <row r="7" spans="1:38" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="52"/>
       <c r="B7" s="52"/>
       <c r="C7" s="52"/>
@@ -2014,9 +1993,7 @@
       <c r="L7" s="52"/>
       <c r="M7" s="52"/>
       <c r="N7" s="52"/>
-      <c r="O7" s="60" t="s">
-        <v>252</v>
-      </c>
+      <c r="O7" s="60"/>
       <c r="P7" s="52"/>
       <c r="R7" s="26"/>
       <c r="S7" s="26"/>
@@ -2035,7 +2012,7 @@
       <c r="AF7" s="61"/>
       <c r="AG7" s="61"/>
     </row>
-    <row r="8" spans="1:38" s="24" customFormat="1">
+    <row r="8" spans="1:38" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52"/>
       <c r="B8" s="52"/>
       <c r="C8" s="52"/>
@@ -2069,7 +2046,7 @@
       <c r="AF8" s="61"/>
       <c r="AG8" s="61"/>
     </row>
-    <row r="9" spans="1:38" s="24" customFormat="1" ht="18.75">
+    <row r="9" spans="1:38" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="52"/>
       <c r="B9" s="52"/>
       <c r="C9" s="52"/>
@@ -2084,9 +2061,7 @@
       <c r="L9" s="52"/>
       <c r="M9" s="52"/>
       <c r="N9" s="52"/>
-      <c r="O9" s="60" t="s">
-        <v>253</v>
-      </c>
+      <c r="O9" s="60"/>
       <c r="P9" s="52"/>
       <c r="R9" s="26"/>
       <c r="S9" s="26"/>
@@ -2105,7 +2080,7 @@
       <c r="AF9" s="61"/>
       <c r="AG9" s="61"/>
     </row>
-    <row r="10" spans="1:38" s="24" customFormat="1" ht="18.75">
+    <row r="10" spans="1:38" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="52"/>
       <c r="B10" s="52"/>
       <c r="C10" s="52"/>
@@ -2120,9 +2095,7 @@
       <c r="L10" s="52"/>
       <c r="M10" s="52"/>
       <c r="N10" s="52"/>
-      <c r="O10" s="60" t="s">
-        <v>254</v>
-      </c>
+      <c r="O10" s="60"/>
       <c r="P10" s="52"/>
       <c r="R10" s="63"/>
       <c r="S10" s="63"/>
@@ -2141,7 +2114,7 @@
       <c r="AF10" s="59"/>
       <c r="AG10" s="59"/>
     </row>
-    <row r="11" spans="1:38" s="24" customFormat="1">
+    <row r="11" spans="1:38" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="52"/>
       <c r="B11" s="52"/>
       <c r="C11" s="52"/>
@@ -2176,7 +2149,7 @@
       <c r="AF11" s="59"/>
       <c r="AG11" s="59"/>
     </row>
-    <row r="12" spans="1:38" s="24" customFormat="1">
+    <row r="12" spans="1:38" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="52"/>
       <c r="B12" s="52"/>
       <c r="C12" s="52"/>
@@ -2212,30 +2185,30 @@
       <c r="AG12" s="59"/>
       <c r="AH12" s="26"/>
     </row>
-    <row r="13" spans="1:38" s="24" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A13" s="111" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="112"/>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="112"/>
-      <c r="N13" s="112"/>
-      <c r="O13" s="112"/>
-      <c r="P13" s="112"/>
-      <c r="Q13" s="112"/>
-      <c r="R13" s="112"/>
-      <c r="S13" s="112"/>
-      <c r="T13" s="112"/>
-      <c r="U13" s="112"/>
+    <row r="13" spans="1:38" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="100"/>
+      <c r="N13" s="100"/>
+      <c r="O13" s="100"/>
+      <c r="P13" s="100"/>
+      <c r="Q13" s="100"/>
+      <c r="R13" s="100"/>
+      <c r="S13" s="100"/>
+      <c r="T13" s="100"/>
+      <c r="U13" s="100"/>
       <c r="V13" s="64"/>
       <c r="W13" s="64"/>
       <c r="X13" s="64"/>
@@ -2249,30 +2222,30 @@
       <c r="AF13" s="64"/>
       <c r="AG13" s="64"/>
     </row>
-    <row r="14" spans="1:38" s="24" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A14" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="B14" s="114"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="114"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="114"/>
-      <c r="T14" s="114"/>
-      <c r="U14" s="114"/>
+    <row r="14" spans="1:38" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="101" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="102"/>
+      <c r="N14" s="102"/>
+      <c r="O14" s="102"/>
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="102"/>
+      <c r="S14" s="102"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="102"/>
       <c r="V14" s="65"/>
       <c r="W14" s="65"/>
       <c r="X14" s="65"/>
@@ -2286,30 +2259,30 @@
       <c r="AF14" s="65"/>
       <c r="AG14" s="65"/>
     </row>
-    <row r="15" spans="1:38" s="24" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A15" s="113" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="114"/>
-      <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="114"/>
-      <c r="S15" s="114"/>
-      <c r="T15" s="114"/>
-      <c r="U15" s="114"/>
+    <row r="15" spans="1:38" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="101" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="102"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="102"/>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="102"/>
+      <c r="S15" s="102"/>
+      <c r="T15" s="102"/>
+      <c r="U15" s="102"/>
       <c r="V15" s="66"/>
       <c r="W15" s="66"/>
       <c r="X15" s="66"/>
@@ -2323,190 +2296,190 @@
       <c r="AF15" s="66"/>
       <c r="AG15" s="66"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="84" t="s">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="104"/>
+      <c r="D16" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="84" t="s">
+      <c r="H16" s="89"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="89"/>
+      <c r="K16" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84" t="s">
+      <c r="L16" s="89"/>
+      <c r="M16" s="89"/>
+      <c r="N16" s="89"/>
+      <c r="O16" s="89"/>
+      <c r="P16" s="89"/>
+      <c r="Q16" s="103" t="s">
+        <v>7</v>
+      </c>
+      <c r="R16" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="84"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="85" t="s">
+      <c r="S16" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="84"/>
-      <c r="P16" s="84"/>
-      <c r="Q16" s="86" t="s">
+      <c r="T16" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="R16" s="103" t="s">
+      <c r="U16" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="S16" s="86" t="s">
+      <c r="V16" s="34"/>
+      <c r="W16" s="80" t="s">
+        <v>164</v>
+      </c>
+      <c r="X16" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y16" s="84"/>
+      <c r="Z16" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA16" s="85"/>
+      <c r="AB16" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="AC16" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD16" s="91" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE16" s="92"/>
+      <c r="AF16" s="91" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG16" s="93"/>
+    </row>
+    <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="89"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="T16" s="103" t="s">
+      <c r="E17" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="U16" s="103" t="s">
+      <c r="F17" s="89"/>
+      <c r="G17" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="V16" s="34"/>
-      <c r="W16" s="87" t="s">
-        <v>172</v>
-      </c>
-      <c r="X16" s="90" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y16" s="91"/>
-      <c r="Z16" s="90" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA16" s="92"/>
-      <c r="AB16" s="93" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC16" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD16" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="AE16" s="97"/>
-      <c r="AF16" s="96" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG16" s="98"/>
-    </row>
-    <row r="17" spans="1:61" ht="15" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="84"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="84" t="s">
+      <c r="H17" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="84" t="s">
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84" t="s">
+      <c r="L17" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="84" t="s">
+      <c r="M17" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="85" t="s">
+      <c r="N17" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="L17" s="85" t="s">
+      <c r="O17" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="M17" s="85" t="s">
+      <c r="P17" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="N17" s="85" t="s">
+      <c r="Q17" s="103"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="34"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y17" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z17" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA17" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB17" s="87"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE17" s="95" t="s">
+        <v>194</v>
+      </c>
+      <c r="AF17" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG17" s="95" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="89"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O17" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="85" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" s="86"/>
-      <c r="R17" s="103"/>
-      <c r="S17" s="86"/>
-      <c r="T17" s="103"/>
-      <c r="U17" s="103"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="88"/>
-      <c r="X17" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y17" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z17" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA17" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB17" s="94"/>
-      <c r="AC17" s="94"/>
-      <c r="AD17" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE17" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF17" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG17" s="100" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="18" spans="1:61" ht="57" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="I18" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="84"/>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="84"/>
-      <c r="O18" s="84"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
+        <v>20</v>
+      </c>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="89"/>
+      <c r="O18" s="89"/>
+      <c r="P18" s="89"/>
+      <c r="Q18" s="89"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="89"/>
+      <c r="T18" s="89"/>
+      <c r="U18" s="89"/>
       <c r="V18" s="35"/>
-      <c r="W18" s="88"/>
-      <c r="X18" s="88"/>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="88"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="94"/>
-      <c r="AC18" s="94"/>
-      <c r="AD18" s="101"/>
-      <c r="AE18" s="101"/>
-      <c r="AF18" s="101"/>
-      <c r="AG18" s="101"/>
-    </row>
-    <row r="19" spans="1:61" s="14" customFormat="1">
+      <c r="W18" s="81"/>
+      <c r="X18" s="81"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="81"/>
+      <c r="AA18" s="81"/>
+      <c r="AB18" s="87"/>
+      <c r="AC18" s="87"/>
+      <c r="AD18" s="96"/>
+      <c r="AE18" s="96"/>
+      <c r="AF18" s="96"/>
+      <c r="AG18" s="96"/>
+    </row>
+    <row r="19" spans="1:61" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>1</v>
       </c>
@@ -2569,27 +2542,27 @@
         <v>21</v>
       </c>
       <c r="V19" s="33"/>
-      <c r="W19" s="89"/>
-      <c r="X19" s="89"/>
-      <c r="Y19" s="89"/>
-      <c r="Z19" s="89"/>
-      <c r="AA19" s="89"/>
-      <c r="AB19" s="95"/>
-      <c r="AC19" s="95"/>
-      <c r="AD19" s="102"/>
-      <c r="AE19" s="102"/>
-      <c r="AF19" s="102"/>
-      <c r="AG19" s="102"/>
+      <c r="W19" s="82"/>
+      <c r="X19" s="82"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82"/>
+      <c r="AB19" s="88"/>
+      <c r="AC19" s="88"/>
+      <c r="AD19" s="97"/>
+      <c r="AE19" s="97"/>
+      <c r="AF19" s="97"/>
+      <c r="AG19" s="97"/>
       <c r="AH19" s="24"/>
       <c r="AI19" s="25"/>
       <c r="AJ19" s="24"/>
       <c r="AK19" s="24"/>
       <c r="AL19" s="24"/>
       <c r="AM19" s="24" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AN19" s="24" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AO19" s="24"/>
       <c r="AP19" s="24"/>
@@ -2613,111 +2586,111 @@
       <c r="BH19" s="24"/>
       <c r="BI19" s="24"/>
     </row>
-    <row r="20" spans="1:61">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q20" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R20" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="M20" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="O20" s="22" t="s">
+      <c r="S20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="T20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q20" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="R20" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="S20" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="T20" s="22" t="s">
-        <v>46</v>
-      </c>
       <c r="U20" s="23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="V20" s="36"/>
       <c r="W20" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="X20" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y20" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z20" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA20" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB20" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="AC20" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD20" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE20" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="X20" s="38" t="s">
+      <c r="AF20" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="Y20" s="38" t="s">
+      <c r="AG20" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="Z20" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA20" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB20" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="AC20" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="AD20" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="AE20" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="AF20" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG20" s="40" t="s">
-        <v>189</v>
-      </c>
       <c r="AI20" s="26" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AJ20" s="26" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AK20" s="26">
         <v>1</v>
       </c>
       <c r="AL20" s="26" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AM20" s="26"/>
       <c r="AN20" s="26"/>
@@ -2726,106 +2699,106 @@
       <c r="AQ20" s="26"/>
       <c r="AR20" s="26"/>
     </row>
-    <row r="21" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A21" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="B21" s="107"/>
+    <row r="21" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="109" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="110"/>
       <c r="C21" s="47"/>
       <c r="D21" s="27"/>
       <c r="E21" s="28"/>
       <c r="F21" s="28"/>
       <c r="G21" s="28" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K21" s="28"/>
       <c r="L21" s="28" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M21" s="28" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N21" s="28" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O21" s="28" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P21" s="28" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q21" s="28"/>
       <c r="R21" s="28" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="S21" s="28"/>
       <c r="T21" s="28" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U21" s="29" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V21" s="41"/>
       <c r="W21" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="X21" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y21" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z21" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA21" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB21" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="AC21" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD21" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE21" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="X21" s="42" t="s">
+      <c r="AF21" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="Y21" s="42" t="s">
+      <c r="AG21" s="42" t="s">
         <v>192</v>
-      </c>
-      <c r="Z21" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA21" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB21" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC21" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD21" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE21" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF21" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG21" s="42" t="s">
-        <v>200</v>
       </c>
       <c r="AH21" s="24"/>
       <c r="AI21" s="24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ21" s="24" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AK21" s="24">
         <v>1</v>
       </c>
       <c r="AL21" s="24" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AM21" s="24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN21" s="24" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AO21" s="24"/>
       <c r="AP21" s="24"/>
@@ -2849,117 +2822,117 @@
       <c r="BH21" s="24"/>
       <c r="BI21" s="24"/>
     </row>
-    <row r="22" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A22" s="104" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="105"/>
+    <row r="22" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="107" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="108"/>
       <c r="C22" s="46"/>
       <c r="D22" s="30"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
       <c r="G22" s="31" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K22" s="31"/>
       <c r="L22" s="31" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M22" s="31" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N22" s="31" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O22" s="31" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P22" s="31" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="31"/>
       <c r="R22" s="31" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="S22" s="31"/>
       <c r="T22" s="31" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U22" s="32" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V22" s="41"/>
       <c r="W22" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="X22" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y22" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z22" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA22" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB22" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="AC22" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD22" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE22" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="X22" s="43" t="s">
+      <c r="AF22" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="Y22" s="43" t="s">
+      <c r="AG22" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="Z22" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA22" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB22" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC22" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD22" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE22" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF22" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG22" s="43" t="s">
-        <v>200</v>
-      </c>
       <c r="AI22" s="24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ22" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK22" s="24">
         <v>1</v>
       </c>
       <c r="AL22" s="24" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AM22" s="24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN22" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AP22" s="24" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ22" s="24" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AR22" s="24">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1">
+    <row r="23" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2995,16 +2968,16 @@
       <c r="AG23" s="44"/>
       <c r="AH23" s="24"/>
       <c r="AI23" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ23" s="49" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="AK23" s="24">
         <v>7</v>
       </c>
       <c r="AL23" s="24" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="AM23" s="24"/>
       <c r="AN23" s="24"/>
@@ -3030,30 +3003,30 @@
       <c r="BH23" s="24"/>
       <c r="BI23" s="24"/>
     </row>
-    <row r="24" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A24" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="83"/>
-      <c r="S24" s="83"/>
-      <c r="T24" s="83"/>
-      <c r="U24" s="83"/>
+    <row r="24" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="112"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="112"/>
+      <c r="R24" s="112"/>
+      <c r="S24" s="112"/>
+      <c r="T24" s="112"/>
+      <c r="U24" s="112"/>
       <c r="V24" s="44"/>
       <c r="W24" s="44"/>
       <c r="X24" s="44"/>
@@ -3067,7 +3040,7 @@
       <c r="AF24" s="44"/>
       <c r="AG24" s="44"/>
     </row>
-    <row r="25" spans="1:61" ht="15.75" customHeight="1">
+    <row r="25" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3102,190 +3075,190 @@
       <c r="AF25" s="45"/>
       <c r="AG25" s="45"/>
     </row>
-    <row r="26" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A26" s="84" t="s">
+    <row r="26" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="104"/>
+      <c r="D26" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="108"/>
-      <c r="D26" s="84" t="s">
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="89"/>
+      <c r="K26" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84" t="s">
+      <c r="L26" s="89"/>
+      <c r="M26" s="89"/>
+      <c r="N26" s="89"/>
+      <c r="O26" s="89"/>
+      <c r="P26" s="89"/>
+      <c r="Q26" s="103" t="s">
+        <v>7</v>
+      </c>
+      <c r="R26" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="85" t="s">
+      <c r="S26" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="L26" s="84"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="84"/>
-      <c r="P26" s="84"/>
-      <c r="Q26" s="86" t="s">
+      <c r="T26" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="R26" s="103" t="s">
+      <c r="U26" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="S26" s="86" t="s">
+      <c r="V26" s="45"/>
+      <c r="W26" s="80" t="s">
+        <v>164</v>
+      </c>
+      <c r="X26" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y26" s="84"/>
+      <c r="Z26" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA26" s="85"/>
+      <c r="AB26" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="AC26" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD26" s="91" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE26" s="92"/>
+      <c r="AF26" s="91" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG26" s="93"/>
+    </row>
+    <row r="27" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="89"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="T26" s="103" t="s">
+      <c r="E27" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="U26" s="103" t="s">
+      <c r="F27" s="89"/>
+      <c r="G27" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="V26" s="45"/>
-      <c r="W26" s="87" t="s">
-        <v>172</v>
-      </c>
-      <c r="X26" s="90" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y26" s="91"/>
-      <c r="Z26" s="90" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA26" s="92"/>
-      <c r="AB26" s="93" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC26" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD26" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="AE26" s="97"/>
-      <c r="AF26" s="96" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG26" s="98"/>
-    </row>
-    <row r="27" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A27" s="84"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="109"/>
-      <c r="D27" s="84" t="s">
+      <c r="H27" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="84" t="s">
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84" t="s">
+      <c r="L27" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="84" t="s">
+      <c r="M27" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="85" t="s">
+      <c r="N27" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="L27" s="85" t="s">
+      <c r="O27" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="85" t="s">
+      <c r="P27" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="N27" s="85" t="s">
+      <c r="Q27" s="103"/>
+      <c r="R27" s="98"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="98"/>
+      <c r="U27" s="98"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="81"/>
+      <c r="X27" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y27" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z27" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA27" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB27" s="87"/>
+      <c r="AC27" s="87"/>
+      <c r="AD27" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE27" s="95" t="s">
+        <v>194</v>
+      </c>
+      <c r="AF27" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG27" s="95" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="89"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O27" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="P27" s="85" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q27" s="86"/>
-      <c r="R27" s="103"/>
-      <c r="S27" s="86"/>
-      <c r="T27" s="103"/>
-      <c r="U27" s="103"/>
-      <c r="V27" s="45"/>
-      <c r="W27" s="88"/>
-      <c r="X27" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y27" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z27" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA27" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB27" s="94"/>
-      <c r="AC27" s="94"/>
-      <c r="AD27" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE27" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF27" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG27" s="100" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="28" spans="1:61" ht="48" customHeight="1">
-      <c r="A28" s="84"/>
-      <c r="B28" s="84"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="84"/>
-      <c r="H28" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="I28" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="84"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="84"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="84"/>
-      <c r="P28" s="84"/>
-      <c r="Q28" s="84"/>
-      <c r="R28" s="84"/>
-      <c r="S28" s="84"/>
-      <c r="T28" s="84"/>
-      <c r="U28" s="84"/>
+        <v>20</v>
+      </c>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="89"/>
+      <c r="N28" s="89"/>
+      <c r="O28" s="89"/>
+      <c r="P28" s="89"/>
+      <c r="Q28" s="89"/>
+      <c r="R28" s="89"/>
+      <c r="S28" s="89"/>
+      <c r="T28" s="89"/>
+      <c r="U28" s="89"/>
       <c r="V28" s="45"/>
-      <c r="W28" s="88"/>
-      <c r="X28" s="88"/>
-      <c r="Y28" s="88"/>
-      <c r="Z28" s="88"/>
-      <c r="AA28" s="88"/>
-      <c r="AB28" s="94"/>
-      <c r="AC28" s="94"/>
-      <c r="AD28" s="101"/>
-      <c r="AE28" s="101"/>
-      <c r="AF28" s="101"/>
-      <c r="AG28" s="101"/>
-    </row>
-    <row r="29" spans="1:61" ht="15.75">
+      <c r="W28" s="81"/>
+      <c r="X28" s="81"/>
+      <c r="Y28" s="81"/>
+      <c r="Z28" s="81"/>
+      <c r="AA28" s="81"/>
+      <c r="AB28" s="87"/>
+      <c r="AC28" s="87"/>
+      <c r="AD28" s="96"/>
+      <c r="AE28" s="96"/>
+      <c r="AF28" s="96"/>
+      <c r="AG28" s="96"/>
+    </row>
+    <row r="29" spans="1:61" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
         <v>1</v>
       </c>
@@ -3348,119 +3321,119 @@
         <v>21</v>
       </c>
       <c r="V29" s="45"/>
-      <c r="W29" s="89"/>
-      <c r="X29" s="89"/>
-      <c r="Y29" s="89"/>
-      <c r="Z29" s="89"/>
-      <c r="AA29" s="89"/>
-      <c r="AB29" s="95"/>
-      <c r="AC29" s="95"/>
-      <c r="AD29" s="102"/>
-      <c r="AE29" s="102"/>
-      <c r="AF29" s="102"/>
-      <c r="AG29" s="102"/>
-    </row>
-    <row r="30" spans="1:61" ht="15.75">
+      <c r="W29" s="82"/>
+      <c r="X29" s="82"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="88"/>
+      <c r="AC29" s="88"/>
+      <c r="AD29" s="97"/>
+      <c r="AE29" s="97"/>
+      <c r="AF29" s="97"/>
+      <c r="AG29" s="97"/>
+    </row>
+    <row r="30" spans="1:61" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="22" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="M30" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="N30" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="O30" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="P30" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="R30" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="S30" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="T30" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="M30" s="22" t="s">
+      <c r="U30" s="23" t="s">
         <v>78</v>
-      </c>
-      <c r="N30" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="O30" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="P30" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q30" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="R30" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="S30" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="T30" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="U30" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="V30" s="45"/>
       <c r="W30" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="X30" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="Y30" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z30" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA30" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB30" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="AC30" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD30" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE30" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="X30" s="38" t="s">
+      <c r="AF30" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="Y30" s="38" t="s">
+      <c r="AG30" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="Z30" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA30" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB30" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="AC30" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="AD30" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="AE30" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AF30" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="AG30" s="40" t="s">
-        <v>221</v>
-      </c>
       <c r="AI30" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ30" s="50" t="s">
         <v>62</v>
-      </c>
-      <c r="AJ30" s="50" t="s">
-        <v>70</v>
       </c>
       <c r="AK30" s="26">
         <v>1</v>
       </c>
       <c r="AL30" s="50" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AM30" s="26"/>
       <c r="AN30" s="26"/>
@@ -3469,123 +3442,123 @@
       <c r="AQ30" s="26"/>
       <c r="AR30" s="26"/>
     </row>
-    <row r="31" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A31" s="80" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="81"/>
+    <row r="31" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="114"/>
       <c r="C31" s="48"/>
       <c r="D31" s="13"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="Q31" s="11"/>
       <c r="R31" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="S31" s="11"/>
       <c r="T31" s="11" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="V31" s="45"/>
       <c r="W31" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="X31" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y31" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z31" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA31" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB31" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="AC31" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD31" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE31" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="X31" s="43" t="s">
+      <c r="AF31" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="Y31" s="43" t="s">
+      <c r="AG31" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="Z31" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA31" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB31" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC31" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD31" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE31" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF31" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG31" s="43" t="s">
-        <v>200</v>
-      </c>
       <c r="AI31" s="24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ31" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK31" s="24">
         <v>1</v>
       </c>
       <c r="AL31" s="49" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="AM31" s="24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN31" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AP31" s="24" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ31" s="49" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="AR31" s="24">
         <v>0</v>
       </c>
       <c r="AS31" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="AT31" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="AT31" s="49" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1">
+    </row>
+    <row r="32" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -3621,16 +3594,16 @@
       <c r="AG32" s="45"/>
       <c r="AH32" s="24"/>
       <c r="AI32" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ32" s="49" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AK32" s="24">
         <v>7</v>
       </c>
       <c r="AL32" s="24" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="AM32" s="24"/>
       <c r="AN32" s="24"/>
@@ -3656,32 +3629,32 @@
       <c r="BH32" s="24"/>
       <c r="BI32" s="24"/>
     </row>
-    <row r="33" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A33" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="83"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="83"/>
-      <c r="R33" s="83"/>
-      <c r="S33" s="83"/>
-      <c r="T33" s="83"/>
-      <c r="U33" s="83"/>
-    </row>
-    <row r="34" spans="1:61" ht="15.75" customHeight="1">
+    <row r="33" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="112"/>
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
+      <c r="J33" s="112"/>
+      <c r="K33" s="112"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="112"/>
+      <c r="R33" s="112"/>
+      <c r="S33" s="112"/>
+      <c r="T33" s="112"/>
+      <c r="U33" s="112"/>
+    </row>
+    <row r="34" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3704,187 +3677,187 @@
       <c r="T34" s="10"/>
       <c r="U34" s="1"/>
     </row>
-    <row r="35" spans="1:61" ht="15" customHeight="1">
-      <c r="A35" s="84" t="s">
+    <row r="35" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="104"/>
+      <c r="D35" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="89"/>
+      <c r="F35" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="108"/>
-      <c r="D35" s="84" t="s">
+      <c r="H35" s="89"/>
+      <c r="I35" s="89"/>
+      <c r="J35" s="89"/>
+      <c r="K35" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84" t="s">
+      <c r="L35" s="89"/>
+      <c r="M35" s="89"/>
+      <c r="N35" s="89"/>
+      <c r="O35" s="89"/>
+      <c r="P35" s="89"/>
+      <c r="Q35" s="103" t="s">
+        <v>7</v>
+      </c>
+      <c r="R35" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="G35" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="H35" s="84"/>
-      <c r="I35" s="84"/>
-      <c r="J35" s="84"/>
-      <c r="K35" s="85" t="s">
+      <c r="S35" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="L35" s="84"/>
-      <c r="M35" s="84"/>
-      <c r="N35" s="84"/>
-      <c r="O35" s="84"/>
-      <c r="P35" s="84"/>
-      <c r="Q35" s="86" t="s">
+      <c r="T35" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="R35" s="103" t="s">
+      <c r="U35" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="S35" s="86" t="s">
+      <c r="W35" s="80" t="s">
+        <v>164</v>
+      </c>
+      <c r="X35" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y35" s="84"/>
+      <c r="Z35" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA35" s="85"/>
+      <c r="AB35" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="AC35" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD35" s="91" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE35" s="92"/>
+      <c r="AF35" s="91" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG35" s="93"/>
+    </row>
+    <row r="36" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A36" s="89"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="T35" s="103" t="s">
+      <c r="E36" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="U35" s="103" t="s">
+      <c r="F36" s="89"/>
+      <c r="G36" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="W35" s="87" t="s">
-        <v>172</v>
-      </c>
-      <c r="X35" s="90" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y35" s="91"/>
-      <c r="Z35" s="90" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA35" s="92"/>
-      <c r="AB35" s="93" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC35" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD35" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="AE35" s="97"/>
-      <c r="AF35" s="96" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG35" s="98"/>
-    </row>
-    <row r="36" spans="1:61">
-      <c r="A36" s="84"/>
-      <c r="B36" s="84"/>
-      <c r="C36" s="109"/>
-      <c r="D36" s="84" t="s">
+      <c r="H36" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="84" t="s">
+      <c r="I36" s="89"/>
+      <c r="J36" s="89"/>
+      <c r="K36" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="F36" s="84"/>
-      <c r="G36" s="84" t="s">
+      <c r="L36" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="84" t="s">
+      <c r="M36" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="I36" s="84"/>
-      <c r="J36" s="84"/>
-      <c r="K36" s="85" t="s">
+      <c r="N36" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="L36" s="85" t="s">
+      <c r="O36" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="85" t="s">
+      <c r="P36" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="N36" s="85" t="s">
+      <c r="Q36" s="103"/>
+      <c r="R36" s="98"/>
+      <c r="S36" s="103"/>
+      <c r="T36" s="98"/>
+      <c r="U36" s="98"/>
+      <c r="W36" s="81"/>
+      <c r="X36" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y36" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z36" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA36" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB36" s="87"/>
+      <c r="AC36" s="87"/>
+      <c r="AD36" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE36" s="95" t="s">
+        <v>194</v>
+      </c>
+      <c r="AF36" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG36" s="95" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:61" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="89"/>
+      <c r="B37" s="89"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="89"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="89"/>
+      <c r="H37" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O36" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="P36" s="85" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q36" s="86"/>
-      <c r="R36" s="103"/>
-      <c r="S36" s="86"/>
-      <c r="T36" s="103"/>
-      <c r="U36" s="103"/>
-      <c r="W36" s="88"/>
-      <c r="X36" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y36" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z36" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA36" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB36" s="94"/>
-      <c r="AC36" s="94"/>
-      <c r="AD36" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE36" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF36" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG36" s="100" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="37" spans="1:61" ht="48" customHeight="1">
-      <c r="A37" s="84"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="110"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="I37" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37" s="84"/>
-      <c r="L37" s="84"/>
-      <c r="M37" s="84"/>
-      <c r="N37" s="84"/>
-      <c r="O37" s="84"/>
-      <c r="P37" s="84"/>
-      <c r="Q37" s="84"/>
-      <c r="R37" s="84"/>
-      <c r="S37" s="84"/>
-      <c r="T37" s="84"/>
-      <c r="U37" s="84"/>
-      <c r="W37" s="88"/>
-      <c r="X37" s="88"/>
-      <c r="Y37" s="88"/>
-      <c r="Z37" s="88"/>
-      <c r="AA37" s="88"/>
-      <c r="AB37" s="94"/>
-      <c r="AC37" s="94"/>
-      <c r="AD37" s="101"/>
-      <c r="AE37" s="101"/>
-      <c r="AF37" s="101"/>
-      <c r="AG37" s="101"/>
-    </row>
-    <row r="38" spans="1:61">
+        <v>20</v>
+      </c>
+      <c r="K37" s="89"/>
+      <c r="L37" s="89"/>
+      <c r="M37" s="89"/>
+      <c r="N37" s="89"/>
+      <c r="O37" s="89"/>
+      <c r="P37" s="89"/>
+      <c r="Q37" s="89"/>
+      <c r="R37" s="89"/>
+      <c r="S37" s="89"/>
+      <c r="T37" s="89"/>
+      <c r="U37" s="89"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="81"/>
+      <c r="Y37" s="81"/>
+      <c r="Z37" s="81"/>
+      <c r="AA37" s="81"/>
+      <c r="AB37" s="87"/>
+      <c r="AC37" s="87"/>
+      <c r="AD37" s="96"/>
+      <c r="AE37" s="96"/>
+      <c r="AF37" s="96"/>
+      <c r="AG37" s="96"/>
+    </row>
+    <row r="38" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <v>1</v>
       </c>
@@ -3946,118 +3919,118 @@
       <c r="U38" s="16">
         <v>21</v>
       </c>
-      <c r="W38" s="89"/>
-      <c r="X38" s="89"/>
-      <c r="Y38" s="89"/>
-      <c r="Z38" s="89"/>
-      <c r="AA38" s="89"/>
-      <c r="AB38" s="95"/>
-      <c r="AC38" s="95"/>
-      <c r="AD38" s="102"/>
-      <c r="AE38" s="102"/>
-      <c r="AF38" s="102"/>
-      <c r="AG38" s="102"/>
-    </row>
-    <row r="39" spans="1:61">
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+      <c r="Z38" s="82"/>
+      <c r="AA38" s="82"/>
+      <c r="AB38" s="88"/>
+      <c r="AC38" s="88"/>
+      <c r="AD38" s="97"/>
+      <c r="AE38" s="97"/>
+      <c r="AF38" s="97"/>
+      <c r="AG38" s="97"/>
+    </row>
+    <row r="39" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="22" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="M39" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="N39" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="O39" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="P39" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q39" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="R39" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="S39" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="T39" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="M39" s="22" t="s">
+      <c r="U39" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="N39" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="O39" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="P39" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q39" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="R39" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="S39" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="T39" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="U39" s="23" t="s">
-        <v>123</v>
-      </c>
       <c r="W39" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="X39" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y39" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z39" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA39" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB39" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="AC39" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="AD39" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE39" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="X39" s="38" t="s">
+      <c r="AF39" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="Y39" s="38" t="s">
+      <c r="AG39" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="Z39" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="AA39" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="AB39" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="AC39" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="AD39" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="AE39" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="AF39" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="AG39" s="40" t="s">
-        <v>232</v>
-      </c>
       <c r="AI39" s="26" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AJ39" s="50" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AK39" s="26">
         <v>1</v>
       </c>
       <c r="AL39" s="50" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AM39" s="26"/>
       <c r="AN39" s="26"/>
@@ -4066,122 +4039,122 @@
       <c r="AQ39" s="26"/>
       <c r="AR39" s="26"/>
     </row>
-    <row r="40" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A40" s="80" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="81"/>
+    <row r="40" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="114"/>
       <c r="C40" s="48"/>
       <c r="D40" s="13"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K40" s="11"/>
       <c r="L40" s="11" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="P40" s="11" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="Q40" s="11"/>
       <c r="R40" s="11" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="S40" s="11"/>
       <c r="T40" s="11" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="W40" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="X40" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y40" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z40" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA40" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB40" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="AC40" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD40" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE40" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="X40" s="43" t="s">
+      <c r="AF40" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="Y40" s="43" t="s">
+      <c r="AG40" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="Z40" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA40" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB40" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC40" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD40" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE40" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF40" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG40" s="43" t="s">
-        <v>200</v>
-      </c>
       <c r="AI40" s="24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ40" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK40" s="24">
         <v>1</v>
       </c>
       <c r="AL40" s="49" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AM40" s="24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN40" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AP40" s="24" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ40" s="49" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AR40" s="24">
         <v>0</v>
       </c>
       <c r="AS40" s="24" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AT40" s="49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -4205,16 +4178,16 @@
       <c r="U41" s="21"/>
       <c r="AH41" s="24"/>
       <c r="AI41" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ41" s="49" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AK41" s="24">
         <v>7</v>
       </c>
       <c r="AL41" s="24" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="AM41" s="24"/>
       <c r="AN41" s="24"/>
@@ -4240,32 +4213,32 @@
       <c r="BH41" s="24"/>
       <c r="BI41" s="24"/>
     </row>
-    <row r="42" spans="1:61" ht="15.75" customHeight="1">
-      <c r="A42" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="83"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="83"/>
-      <c r="T42" s="83"/>
-      <c r="U42" s="83"/>
-    </row>
-    <row r="43" spans="1:61" ht="15.75" customHeight="1">
+    <row r="42" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="111" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="112"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="112"/>
+      <c r="G42" s="112"/>
+      <c r="H42" s="112"/>
+      <c r="I42" s="112"/>
+      <c r="J42" s="112"/>
+      <c r="K42" s="112"/>
+      <c r="L42" s="112"/>
+      <c r="M42" s="112"/>
+      <c r="N42" s="112"/>
+      <c r="O42" s="112"/>
+      <c r="P42" s="112"/>
+      <c r="Q42" s="112"/>
+      <c r="R42" s="112"/>
+      <c r="S42" s="112"/>
+      <c r="T42" s="112"/>
+      <c r="U42" s="112"/>
+    </row>
+    <row r="43" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -4288,187 +4261,187 @@
       <c r="T43" s="10"/>
       <c r="U43" s="1"/>
     </row>
-    <row r="44" spans="1:61" ht="15" customHeight="1">
-      <c r="A44" s="84" t="s">
+    <row r="44" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="104"/>
+      <c r="D44" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="108"/>
-      <c r="D44" s="84" t="s">
+      <c r="H44" s="89"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="E44" s="84"/>
-      <c r="F44" s="84" t="s">
+      <c r="L44" s="89"/>
+      <c r="M44" s="89"/>
+      <c r="N44" s="89"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="89"/>
+      <c r="Q44" s="103" t="s">
+        <v>7</v>
+      </c>
+      <c r="R44" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="H44" s="84"/>
-      <c r="I44" s="84"/>
-      <c r="J44" s="84"/>
-      <c r="K44" s="85" t="s">
+      <c r="S44" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="84"/>
-      <c r="M44" s="84"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="84"/>
-      <c r="P44" s="84"/>
-      <c r="Q44" s="86" t="s">
+      <c r="T44" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="R44" s="103" t="s">
+      <c r="U44" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="S44" s="86" t="s">
+      <c r="W44" s="80" t="s">
+        <v>164</v>
+      </c>
+      <c r="X44" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y44" s="84"/>
+      <c r="Z44" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA44" s="85"/>
+      <c r="AB44" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="AC44" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD44" s="91" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE44" s="92"/>
+      <c r="AF44" s="91" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG44" s="93"/>
+    </row>
+    <row r="45" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A45" s="89"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="T44" s="103" t="s">
+      <c r="E45" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="U44" s="103" t="s">
+      <c r="F45" s="89"/>
+      <c r="G45" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="W44" s="87" t="s">
-        <v>172</v>
-      </c>
-      <c r="X44" s="90" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y44" s="91"/>
-      <c r="Z44" s="90" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA44" s="92"/>
-      <c r="AB44" s="93" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC44" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD44" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="AE44" s="97"/>
-      <c r="AF44" s="96" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG44" s="98"/>
-    </row>
-    <row r="45" spans="1:61">
-      <c r="A45" s="84"/>
-      <c r="B45" s="84"/>
-      <c r="C45" s="109"/>
-      <c r="D45" s="84" t="s">
+      <c r="H45" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="84" t="s">
+      <c r="I45" s="89"/>
+      <c r="J45" s="89"/>
+      <c r="K45" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="84"/>
-      <c r="G45" s="84" t="s">
+      <c r="L45" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="H45" s="84" t="s">
+      <c r="M45" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="84"/>
-      <c r="J45" s="84"/>
-      <c r="K45" s="85" t="s">
+      <c r="N45" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="L45" s="85" t="s">
+      <c r="O45" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="M45" s="85" t="s">
+      <c r="P45" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="N45" s="85" t="s">
+      <c r="Q45" s="103"/>
+      <c r="R45" s="98"/>
+      <c r="S45" s="103"/>
+      <c r="T45" s="98"/>
+      <c r="U45" s="98"/>
+      <c r="W45" s="81"/>
+      <c r="X45" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y45" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z45" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA45" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB45" s="87"/>
+      <c r="AC45" s="87"/>
+      <c r="AD45" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE45" s="95" t="s">
+        <v>194</v>
+      </c>
+      <c r="AF45" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG45" s="95" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:61" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="89"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="106"/>
+      <c r="D46" s="89"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="89"/>
+      <c r="H46" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O45" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="P45" s="85" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q45" s="86"/>
-      <c r="R45" s="103"/>
-      <c r="S45" s="86"/>
-      <c r="T45" s="103"/>
-      <c r="U45" s="103"/>
-      <c r="W45" s="88"/>
-      <c r="X45" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y45" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z45" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA45" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB45" s="94"/>
-      <c r="AC45" s="94"/>
-      <c r="AD45" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE45" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF45" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG45" s="100" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="46" spans="1:61" ht="48" customHeight="1">
-      <c r="A46" s="84"/>
-      <c r="B46" s="84"/>
-      <c r="C46" s="110"/>
-      <c r="D46" s="84"/>
-      <c r="E46" s="84"/>
-      <c r="F46" s="84"/>
-      <c r="G46" s="84"/>
-      <c r="H46" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="I46" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K46" s="84"/>
-      <c r="L46" s="84"/>
-      <c r="M46" s="84"/>
-      <c r="N46" s="84"/>
-      <c r="O46" s="84"/>
-      <c r="P46" s="84"/>
-      <c r="Q46" s="84"/>
-      <c r="R46" s="84"/>
-      <c r="S46" s="84"/>
-      <c r="T46" s="84"/>
-      <c r="U46" s="84"/>
-      <c r="W46" s="88"/>
-      <c r="X46" s="88"/>
-      <c r="Y46" s="88"/>
-      <c r="Z46" s="88"/>
-      <c r="AA46" s="88"/>
-      <c r="AB46" s="94"/>
-      <c r="AC46" s="94"/>
-      <c r="AD46" s="101"/>
-      <c r="AE46" s="101"/>
-      <c r="AF46" s="101"/>
-      <c r="AG46" s="101"/>
-    </row>
-    <row r="47" spans="1:61">
+        <v>20</v>
+      </c>
+      <c r="K46" s="89"/>
+      <c r="L46" s="89"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="89"/>
+      <c r="O46" s="89"/>
+      <c r="P46" s="89"/>
+      <c r="Q46" s="89"/>
+      <c r="R46" s="89"/>
+      <c r="S46" s="89"/>
+      <c r="T46" s="89"/>
+      <c r="U46" s="89"/>
+      <c r="W46" s="81"/>
+      <c r="X46" s="81"/>
+      <c r="Y46" s="81"/>
+      <c r="Z46" s="81"/>
+      <c r="AA46" s="81"/>
+      <c r="AB46" s="87"/>
+      <c r="AC46" s="87"/>
+      <c r="AD46" s="96"/>
+      <c r="AE46" s="96"/>
+      <c r="AF46" s="96"/>
+      <c r="AG46" s="96"/>
+    </row>
+    <row r="47" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>1</v>
       </c>
@@ -4530,118 +4503,118 @@
       <c r="U47" s="16">
         <v>21</v>
       </c>
-      <c r="W47" s="89"/>
-      <c r="X47" s="89"/>
-      <c r="Y47" s="89"/>
-      <c r="Z47" s="89"/>
-      <c r="AA47" s="89"/>
-      <c r="AB47" s="95"/>
-      <c r="AC47" s="95"/>
-      <c r="AD47" s="102"/>
-      <c r="AE47" s="102"/>
-      <c r="AF47" s="102"/>
-      <c r="AG47" s="102"/>
-    </row>
-    <row r="48" spans="1:61">
+      <c r="W47" s="82"/>
+      <c r="X47" s="82"/>
+      <c r="Y47" s="82"/>
+      <c r="Z47" s="82"/>
+      <c r="AA47" s="82"/>
+      <c r="AB47" s="88"/>
+      <c r="AC47" s="88"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="97"/>
+      <c r="AF47" s="97"/>
+      <c r="AG47" s="97"/>
+    </row>
+    <row r="48" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="22" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="M48" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="N48" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="O48" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="P48" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q48" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="R48" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="S48" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="T48" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="M48" s="22" t="s">
+      <c r="U48" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="N48" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="O48" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="P48" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q48" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="R48" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="S48" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="T48" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="U48" s="23" t="s">
-        <v>150</v>
-      </c>
       <c r="W48" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="X48" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y48" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z48" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA48" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB48" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC48" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD48" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE48" s="40" t="s">
         <v>233</v>
       </c>
-      <c r="X48" s="38" t="s">
+      <c r="AF48" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="Y48" s="38" t="s">
+      <c r="AG48" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="Z48" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA48" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB48" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC48" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="AD48" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE48" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="AF48" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="AG48" s="40" t="s">
-        <v>243</v>
-      </c>
       <c r="AI48" s="26" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AJ48" s="50" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="AK48" s="26">
         <v>1</v>
       </c>
       <c r="AL48" s="50" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="AM48" s="26"/>
       <c r="AN48" s="26"/>
@@ -4650,122 +4623,122 @@
       <c r="AQ48" s="26"/>
       <c r="AR48" s="26"/>
     </row>
-    <row r="49" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A49" s="80" t="s">
-        <v>26</v>
-      </c>
-      <c r="B49" s="81"/>
+    <row r="49" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="114"/>
       <c r="C49" s="48"/>
       <c r="D49" s="13"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="11" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="11" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="M49" s="11" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="P49" s="11" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="S49" s="11"/>
       <c r="T49" s="11" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U49" s="12" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="W49" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="X49" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y49" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z49" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA49" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB49" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="AC49" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD49" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE49" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="X49" s="43" t="s">
+      <c r="AF49" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="Y49" s="43" t="s">
+      <c r="AG49" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="Z49" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA49" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB49" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC49" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD49" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE49" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF49" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG49" s="43" t="s">
-        <v>200</v>
-      </c>
       <c r="AI49" s="24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ49" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK49" s="24">
         <v>1</v>
       </c>
       <c r="AL49" s="49" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="AM49" s="24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN49" s="24" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AP49" s="24" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ49" s="49" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="AR49" s="24">
         <v>0</v>
       </c>
       <c r="AS49" s="24" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AT49" s="49" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="1:46" ht="15.75" customHeight="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -4786,19 +4759,19 @@
       <c r="T50" s="1"/>
       <c r="U50" s="5"/>
       <c r="AI50" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ50" s="49" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="AK50" s="24">
         <v>14</v>
       </c>
       <c r="AL50" s="24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:46" s="24" customFormat="1" ht="18.75">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:46" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B51" s="67"/>
       <c r="C51" s="67"/>
       <c r="D51" s="67"/>
@@ -4820,7 +4793,7 @@
       <c r="T51" s="67"/>
       <c r="U51" s="67"/>
     </row>
-    <row r="52" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
+    <row r="52" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="68"/>
       <c r="B52" s="69"/>
       <c r="C52" s="69"/>
@@ -4843,11 +4816,11 @@
       <c r="T52" s="69"/>
       <c r="U52" s="70"/>
     </row>
-    <row r="53" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A53" s="68"/>
-      <c r="B53" s="72" t="s">
-        <v>30</v>
-      </c>
+    <row r="53" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A53" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="B53" s="72"/>
       <c r="C53" s="72"/>
       <c r="D53" s="72"/>
       <c r="E53" s="72"/>
@@ -4857,24 +4830,18 @@
       <c r="I53" s="72"/>
       <c r="J53" s="72"/>
       <c r="K53" s="72"/>
-      <c r="L53" s="72" t="s">
-        <v>32</v>
-      </c>
+      <c r="L53" s="72"/>
       <c r="M53" s="72"/>
       <c r="N53" s="73"/>
       <c r="O53" s="73"/>
       <c r="P53" s="74"/>
       <c r="Q53" s="74"/>
       <c r="R53" s="72"/>
-      <c r="S53" s="69"/>
       <c r="T53" s="73"/>
       <c r="U53" s="73"/>
     </row>
-    <row r="54" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A54" s="68"/>
-      <c r="B54" s="72" t="s">
-        <v>31</v>
-      </c>
+    <row r="54" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B54" s="72"/>
       <c r="C54" s="72"/>
       <c r="D54" s="72"/>
       <c r="E54" s="72"/>
@@ -4884,26 +4851,20 @@
       <c r="I54" s="72"/>
       <c r="J54" s="72"/>
       <c r="K54" s="72"/>
-      <c r="L54" s="75" t="s">
-        <v>33</v>
-      </c>
+      <c r="L54" s="75"/>
       <c r="M54" s="75"/>
       <c r="N54" s="75"/>
       <c r="O54" s="75"/>
       <c r="P54" s="75"/>
-      <c r="Q54" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="R54" s="69"/>
-      <c r="S54" s="69"/>
+      <c r="Q54" s="72"/>
       <c r="T54" s="75"/>
       <c r="U54" s="72"/>
-    </row>
-    <row r="55" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A55" s="68"/>
-      <c r="B55" s="72" t="s">
-        <v>3</v>
-      </c>
+      <c r="W54" s="69" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B55" s="72"/>
       <c r="C55" s="72"/>
       <c r="D55" s="72"/>
       <c r="E55" s="72"/>
@@ -4919,13 +4880,19 @@
       <c r="O55" s="76"/>
       <c r="P55" s="72"/>
       <c r="Q55" s="72"/>
-      <c r="R55" s="69"/>
-      <c r="S55" s="69"/>
       <c r="T55" s="72"/>
       <c r="U55" s="72"/>
-    </row>
-    <row r="56" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A56" s="68"/>
+      <c r="W55" s="69" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA55" s="69" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A56" s="69" t="s">
+        <v>242</v>
+      </c>
       <c r="B56" s="72"/>
       <c r="C56" s="72"/>
       <c r="D56" s="72"/>
@@ -4942,16 +4909,11 @@
       <c r="O56" s="73"/>
       <c r="P56" s="74"/>
       <c r="Q56" s="72"/>
-      <c r="R56" s="69"/>
-      <c r="S56" s="69"/>
       <c r="T56" s="72"/>
       <c r="U56" s="72"/>
     </row>
-    <row r="57" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A57" s="68"/>
-      <c r="B57" s="72" t="s">
-        <v>34</v>
-      </c>
+    <row r="57" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B57" s="72"/>
       <c r="C57" s="72"/>
       <c r="D57" s="72"/>
       <c r="E57" s="72"/>
@@ -4961,23 +4923,19 @@
       <c r="I57" s="72"/>
       <c r="J57" s="72"/>
       <c r="K57" s="72"/>
-      <c r="L57" s="75" t="s">
-        <v>246</v>
-      </c>
+      <c r="L57" s="75"/>
       <c r="M57" s="75"/>
       <c r="N57" s="75"/>
       <c r="O57" s="75"/>
       <c r="P57" s="75"/>
-      <c r="Q57" s="73" t="s">
-        <v>247</v>
-      </c>
-      <c r="R57" s="69"/>
-      <c r="S57" s="69"/>
+      <c r="Q57" s="73"/>
       <c r="T57" s="72"/>
       <c r="U57" s="72"/>
     </row>
-    <row r="58" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A58" s="68"/>
+    <row r="58" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A58" s="69" t="s">
+        <v>27</v>
+      </c>
       <c r="B58" s="72"/>
       <c r="C58" s="72"/>
       <c r="D58" s="72"/>
@@ -4994,16 +4952,17 @@
       <c r="O58" s="76"/>
       <c r="P58" s="72"/>
       <c r="Q58" s="72"/>
-      <c r="R58" s="69"/>
-      <c r="S58" s="69"/>
       <c r="T58" s="72"/>
       <c r="U58" s="72"/>
-    </row>
-    <row r="59" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A59" s="68"/>
-      <c r="B59" s="72" t="s">
-        <v>35</v>
-      </c>
+      <c r="W58" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA58" s="69" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="59" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B59" s="72"/>
       <c r="C59" s="72"/>
       <c r="D59" s="72"/>
       <c r="E59" s="72"/>
@@ -5019,13 +4978,13 @@
       <c r="O59" s="60"/>
       <c r="P59" s="60"/>
       <c r="Q59" s="72"/>
-      <c r="R59" s="69"/>
-      <c r="S59" s="69"/>
       <c r="T59" s="60"/>
       <c r="U59" s="78"/>
     </row>
-    <row r="60" spans="1:46" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A60" s="68"/>
+    <row r="60" spans="1:46" s="69" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A60" s="69" t="s">
+        <v>243</v>
+      </c>
       <c r="B60" s="72"/>
       <c r="C60" s="72"/>
       <c r="D60" s="72"/>
@@ -5042,15 +5001,17 @@
       <c r="O60" s="72"/>
       <c r="P60" s="72"/>
       <c r="Q60" s="72"/>
-      <c r="R60" s="69"/>
-      <c r="S60" s="69"/>
       <c r="T60" s="60"/>
       <c r="U60" s="72"/>
-    </row>
-    <row r="61" spans="1:46" s="26" customFormat="1" ht="18.75">
-      <c r="B61" s="72" t="s">
-        <v>255</v>
-      </c>
+      <c r="W60" s="69" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA60" s="69" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="1:46" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B61" s="72"/>
       <c r="C61" s="72"/>
       <c r="D61" s="72"/>
       <c r="E61" s="72"/>
@@ -5060,22 +5021,18 @@
       <c r="I61" s="72"/>
       <c r="J61" s="72"/>
       <c r="K61" s="72"/>
-      <c r="L61" s="79" t="s">
-        <v>256</v>
-      </c>
+      <c r="L61" s="79"/>
       <c r="M61" s="79"/>
       <c r="N61" s="79"/>
       <c r="O61" s="72"/>
       <c r="P61" s="72"/>
-      <c r="Q61" s="79" t="s">
-        <v>257</v>
-      </c>
+      <c r="Q61" s="79"/>
       <c r="R61" s="69"/>
       <c r="S61" s="69"/>
       <c r="T61" s="79"/>
       <c r="U61" s="79"/>
     </row>
-    <row r="62" spans="1:46" s="26" customFormat="1" ht="18.75">
+    <row r="62" spans="1:46" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B62" s="69"/>
       <c r="C62" s="69"/>
       <c r="D62" s="69"/>
@@ -5097,62 +5054,117 @@
       <c r="T62" s="69"/>
       <c r="U62" s="69"/>
     </row>
-    <row r="63" spans="1:46" s="26" customFormat="1">
+    <row r="63" spans="1:46" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AM63" s="26" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AN63" s="50" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:46">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="64" spans="1:46" x14ac:dyDescent="0.25">
       <c r="AI64" s="51" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="159">
-    <mergeCell ref="W16:W19"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AB16:AB19"/>
-    <mergeCell ref="AC16:AC19"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="AD16:AE16"/>
-    <mergeCell ref="AF16:AG16"/>
-    <mergeCell ref="X17:X19"/>
-    <mergeCell ref="Y17:Y19"/>
-    <mergeCell ref="Z17:Z19"/>
-    <mergeCell ref="AA17:AA19"/>
-    <mergeCell ref="AD17:AD19"/>
-    <mergeCell ref="AE17:AE19"/>
-    <mergeCell ref="AF17:AF19"/>
-    <mergeCell ref="AG17:AG19"/>
-    <mergeCell ref="U16:U18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="A13:U13"/>
-    <mergeCell ref="A15:U15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="K16:P16"/>
-    <mergeCell ref="Q16:Q18"/>
-    <mergeCell ref="R16:R18"/>
-    <mergeCell ref="S16:S18"/>
-    <mergeCell ref="T16:T18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="A14:U14"/>
-    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A33:U33"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="K35:P35"/>
+    <mergeCell ref="Q35:Q37"/>
+    <mergeCell ref="W44:W47"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="W35:W38"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="W26:W29"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="Z44:AA44"/>
+    <mergeCell ref="Z35:AA35"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="R35:R37"/>
+    <mergeCell ref="S35:S37"/>
+    <mergeCell ref="T35:T37"/>
+    <mergeCell ref="U35:U37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="AB44:AB47"/>
+    <mergeCell ref="AC44:AC47"/>
+    <mergeCell ref="AD44:AE44"/>
+    <mergeCell ref="AF44:AG44"/>
+    <mergeCell ref="X45:X47"/>
+    <mergeCell ref="Y45:Y47"/>
+    <mergeCell ref="Z45:Z47"/>
+    <mergeCell ref="AA45:AA47"/>
+    <mergeCell ref="AD45:AD47"/>
+    <mergeCell ref="AE45:AE47"/>
+    <mergeCell ref="AF45:AF47"/>
+    <mergeCell ref="AG45:AG47"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="AB35:AB38"/>
+    <mergeCell ref="AC35:AC38"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="AF35:AG35"/>
+    <mergeCell ref="X36:X38"/>
+    <mergeCell ref="Y36:Y38"/>
+    <mergeCell ref="Z36:Z38"/>
+    <mergeCell ref="AA36:AA38"/>
+    <mergeCell ref="AD36:AD38"/>
+    <mergeCell ref="AE36:AE38"/>
+    <mergeCell ref="AF36:AF38"/>
+    <mergeCell ref="AG36:AG38"/>
+    <mergeCell ref="AB26:AB29"/>
+    <mergeCell ref="AC26:AC29"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="AF26:AG26"/>
+    <mergeCell ref="X27:X29"/>
+    <mergeCell ref="Y27:Y29"/>
+    <mergeCell ref="Z27:Z29"/>
+    <mergeCell ref="AA27:AA29"/>
+    <mergeCell ref="AD27:AD29"/>
+    <mergeCell ref="AE27:AE29"/>
+    <mergeCell ref="AF27:AF29"/>
+    <mergeCell ref="AG27:AG29"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A42:U42"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="K44:P44"/>
+    <mergeCell ref="Q44:Q46"/>
+    <mergeCell ref="R44:R46"/>
+    <mergeCell ref="S44:S46"/>
+    <mergeCell ref="T44:T46"/>
+    <mergeCell ref="U44:U46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="E45:E46"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="B26:B28"/>
@@ -5177,101 +5189,46 @@
     <mergeCell ref="T26:T28"/>
     <mergeCell ref="A24:U24"/>
     <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="L45:L46"/>
-    <mergeCell ref="M45:M46"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A42:U42"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="K44:P44"/>
-    <mergeCell ref="Q44:Q46"/>
-    <mergeCell ref="R44:R46"/>
-    <mergeCell ref="S44:S46"/>
-    <mergeCell ref="T44:T46"/>
-    <mergeCell ref="U44:U46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="AB26:AB29"/>
-    <mergeCell ref="AC26:AC29"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="AF26:AG26"/>
-    <mergeCell ref="X27:X29"/>
-    <mergeCell ref="Y27:Y29"/>
-    <mergeCell ref="Z27:Z29"/>
-    <mergeCell ref="AA27:AA29"/>
-    <mergeCell ref="AD27:AD29"/>
-    <mergeCell ref="AE27:AE29"/>
-    <mergeCell ref="AF27:AF29"/>
-    <mergeCell ref="AG27:AG29"/>
-    <mergeCell ref="AB35:AB38"/>
-    <mergeCell ref="AC35:AC38"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="AF35:AG35"/>
-    <mergeCell ref="X36:X38"/>
-    <mergeCell ref="Y36:Y38"/>
-    <mergeCell ref="Z36:Z38"/>
-    <mergeCell ref="AA36:AA38"/>
-    <mergeCell ref="AD36:AD38"/>
-    <mergeCell ref="AE36:AE38"/>
-    <mergeCell ref="AF36:AF38"/>
-    <mergeCell ref="AG36:AG38"/>
-    <mergeCell ref="AB44:AB47"/>
-    <mergeCell ref="AC44:AC47"/>
-    <mergeCell ref="AD44:AE44"/>
-    <mergeCell ref="AF44:AG44"/>
-    <mergeCell ref="X45:X47"/>
-    <mergeCell ref="Y45:Y47"/>
-    <mergeCell ref="Z45:Z47"/>
-    <mergeCell ref="AA45:AA47"/>
-    <mergeCell ref="AD45:AD47"/>
-    <mergeCell ref="AE45:AE47"/>
-    <mergeCell ref="AF45:AF47"/>
-    <mergeCell ref="AG45:AG47"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="W35:W38"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="W26:W29"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="Z44:AA44"/>
-    <mergeCell ref="Z35:AA35"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="R35:R37"/>
-    <mergeCell ref="S35:S37"/>
-    <mergeCell ref="T35:T37"/>
-    <mergeCell ref="U35:U37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:U33"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="K35:P35"/>
-    <mergeCell ref="Q35:Q37"/>
-    <mergeCell ref="W44:W47"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="A15:U15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="K16:P16"/>
+    <mergeCell ref="Q16:Q18"/>
+    <mergeCell ref="R16:R18"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="T16:T18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="A14:U14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="AD16:AE16"/>
+    <mergeCell ref="AF16:AG16"/>
+    <mergeCell ref="X17:X19"/>
+    <mergeCell ref="Y17:Y19"/>
+    <mergeCell ref="Z17:Z19"/>
+    <mergeCell ref="AA17:AA19"/>
+    <mergeCell ref="AD17:AD19"/>
+    <mergeCell ref="AE17:AE19"/>
+    <mergeCell ref="AF17:AF19"/>
+    <mergeCell ref="AG17:AG19"/>
+    <mergeCell ref="W16:W19"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AB16:AB19"/>
+    <mergeCell ref="AC16:AC19"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="U16:U18"/>
   </mergeCells>
   <pageMargins left="0.70866141732282995" right="0.70866141732282995" top="0.74803149606299002" bottom="0.74803149606299002" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup scale="28" fitToHeight="500" orientation="portrait" r:id="rId1"/>
